--- a/Greenhouse_Sales_Book.xlsx
+++ b/Greenhouse_Sales_Book.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="6540" windowHeight="6945" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6975" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Market prices" sheetId="1" r:id="rId1"/>
@@ -17,8 +17,10 @@
     <sheet name="Scenarios Profitability Tracker" sheetId="3" r:id="rId3"/>
     <sheet name="Guide" sheetId="4" state="hidden" r:id="rId4"/>
     <sheet name="Weighing Reference" sheetId="5" r:id="rId5"/>
+    <sheet name="Production Tracker" sheetId="6" r:id="rId6"/>
+    <sheet name="Harvest Log" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcMode="manual"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="cXMLLrwEbY8wU2GhX23sLfkQvgClYDZjbwSnC6gqBeQ="/>
@@ -121,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="134">
   <si>
     <t>MARKET SURVEY - Greenhouse Project</t>
   </si>
@@ -561,6 +563,54 @@
   <si>
     <t>pieces</t>
   </si>
+  <si>
+    <t xml:space="preserve">Used vehicle hired by FOOP </t>
+  </si>
+  <si>
+    <t>Crop</t>
+  </si>
+  <si>
+    <t>Date Planted</t>
+  </si>
+  <si>
+    <t>Rows</t>
+  </si>
+  <si>
+    <t>Total Plants</t>
+  </si>
+  <si>
+    <t>Expected Harvest (kg)</t>
+  </si>
+  <si>
+    <t>First Harvest Date</t>
+  </si>
+  <si>
+    <t>Last Harvest Date</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Kg Harvested</t>
+  </si>
+  <si>
+    <t>Growing</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Nursery Greenhouse</t>
+  </si>
+  <si>
+    <t>Production Greenhouse</t>
+  </si>
+  <si>
+    <t>African Hot Pepper</t>
+  </si>
+  <si>
+    <t>Outdoor Production</t>
+  </si>
 </sst>
 </file>
 
@@ -575,11 +625,18 @@
     <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -689,6 +746,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -886,168 +951,173 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="7" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="7" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="15" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="12" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="7" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="16" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="17" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="18" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="5" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="16" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="8" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="13" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="8" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="8" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="7" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="17" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="18" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="19" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="6" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="8" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1278,20 +1348,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="74"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="75"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -1308,20 +1378,20 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="75"/>
     </row>
     <row r="3" spans="1:26" ht="42" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -4190,24 +4260,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="30" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="74"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="75"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
@@ -4221,21 +4291,21 @@
       <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="75"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
@@ -4331,7 +4401,9 @@
         <f t="shared" ref="L4:L18" si="3">J4*K4</f>
         <v>175</v>
       </c>
-      <c r="M4" s="4"/>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
       <c r="N4" s="4">
         <f t="shared" ref="N4:N26" si="4">L4-M4</f>
         <v>175</v>
@@ -4340,7 +4412,9 @@
         <f t="shared" ref="O4:O26" si="5">N4/E4</f>
         <v>87.5</v>
       </c>
-      <c r="P4" s="4"/>
+      <c r="P4" s="4" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="5" spans="1:27">
       <c r="A5" s="14">
@@ -4383,7 +4457,9 @@
         <f t="shared" si="3"/>
         <v>85</v>
       </c>
-      <c r="M5" s="4"/>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
       <c r="N5" s="4">
         <f t="shared" si="4"/>
         <v>85</v>
@@ -4392,7 +4468,9 @@
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="P5" s="4"/>
+      <c r="P5" s="4" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="6" spans="1:27">
       <c r="A6" s="14">
@@ -4435,7 +4513,9 @@
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="M6" s="4"/>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
       <c r="N6" s="4">
         <f t="shared" si="4"/>
         <v>44</v>
@@ -4444,7 +4524,9 @@
         <f t="shared" si="5"/>
         <v>4.1904761904761907</v>
       </c>
-      <c r="P6" s="4"/>
+      <c r="P6" s="4" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="7" spans="1:27">
       <c r="A7" s="14">
@@ -4487,7 +4569,9 @@
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
-      <c r="M7" s="4"/>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
       <c r="N7" s="4">
         <f t="shared" si="4"/>
         <v>140</v>
@@ -4496,7 +4580,9 @@
         <f t="shared" si="5"/>
         <v>46.666666666666664</v>
       </c>
-      <c r="P7" s="4"/>
+      <c r="P7" s="4" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="8" spans="1:27">
       <c r="A8" s="16">
@@ -6734,24 +6820,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="81"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
@@ -6764,52 +6850,52 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="82" t="s">
+      <c r="B3" s="74"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="73"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="83" t="s">
+      <c r="E3" s="74"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="73"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="84" t="s">
+      <c r="H3" s="74"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="73"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="85" t="s">
+      <c r="K3" s="74"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="86" t="s">
         <v>77</v>
       </c>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="74"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="75"/>
     </row>
     <row r="4" spans="1:26" ht="42" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -7131,11 +7217,11 @@
       <c r="P9" s="4"/>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="73"/>
-      <c r="C10" s="74"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="75"/>
       <c r="D10" s="37"/>
       <c r="E10" s="37"/>
       <c r="F10" s="38">
@@ -7218,11 +7304,11 @@
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="73"/>
-      <c r="C12" s="74"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="75"/>
       <c r="D12" s="37"/>
       <c r="E12" s="37"/>
       <c r="F12" s="38">
@@ -7482,11 +7568,11 @@
       <c r="P16" s="4"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="74"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="75"/>
       <c r="D17" s="46"/>
       <c r="E17" s="46"/>
       <c r="F17" s="47">
@@ -7747,11 +7833,11 @@
       <c r="P21" s="4"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="73"/>
-      <c r="C22" s="74"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="75"/>
       <c r="D22" s="37"/>
       <c r="E22" s="37"/>
       <c r="F22" s="38">
@@ -7953,11 +8039,11 @@
       <c r="P25" s="4"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="77" t="s">
+      <c r="A26" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="73"/>
-      <c r="C26" s="74"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="75"/>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
       <c r="F26" s="38">
@@ -8040,11 +8126,11 @@
       <c r="P27" s="4"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="73"/>
-      <c r="C28" s="74"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="75"/>
       <c r="D28" s="37"/>
       <c r="E28" s="37"/>
       <c r="F28" s="38">
@@ -8246,11 +8332,11 @@
       <c r="P31" s="4"/>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="77" t="s">
+      <c r="A32" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="73"/>
-      <c r="C32" s="74"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="75"/>
       <c r="D32" s="52"/>
       <c r="E32" s="37"/>
       <c r="F32" s="38">
@@ -8452,11 +8538,11 @@
       <c r="P35" s="4"/>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="77" t="s">
+      <c r="A36" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="73"/>
-      <c r="C36" s="74"/>
+      <c r="B36" s="74"/>
+      <c r="C36" s="75"/>
       <c r="D36" s="52"/>
       <c r="E36" s="37"/>
       <c r="F36" s="47">
@@ -10038,16 +10124,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="91"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="92"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -10244,14 +10330,14 @@
       <c r="H16" s="22"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="92"/>
-      <c r="B17" s="87"/>
-      <c r="C17" s="87"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="87"/>
-      <c r="H17" s="87"/>
+      <c r="A17" s="93"/>
+      <c r="B17" s="88"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="88"/>
     </row>
     <row r="18" spans="1:8" ht="42" customHeight="1">
       <c r="A18" s="59"/>
@@ -11613,16 +11699,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="74"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -11643,40 +11729,40 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="76" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:26" ht="29.25" customHeight="1">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:26" ht="29.25" customHeight="1">
-      <c r="A4" s="95" t="s">
+      <c r="A4" s="96" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:26" ht="42" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -12140,16 +12226,16 @@
       <c r="H22" s="67"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="96" t="s">
+      <c r="A23" s="97" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="74"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="75"/>
     </row>
     <row r="24" spans="1:12" ht="42" customHeight="1">
       <c r="A24" s="70" t="s">
@@ -13560,4 +13646,225 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" style="72" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="98" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="98" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="98" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" s="98" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" s="98" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" s="98" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1" s="98" t="s">
+        <v>125</v>
+      </c>
+      <c r="I1" s="98" t="s">
+        <v>126</v>
+      </c>
+      <c r="J1" s="98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="99" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="100">
+        <v>46063</v>
+      </c>
+      <c r="C2" s="101" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>106</v>
+      </c>
+      <c r="F2">
+        <v>477</v>
+      </c>
+      <c r="I2" s="99" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="99" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="100">
+        <v>46078</v>
+      </c>
+      <c r="C3" s="99" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>58</v>
+      </c>
+      <c r="F3">
+        <v>261</v>
+      </c>
+      <c r="I3" s="99" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="100">
+        <v>46065</v>
+      </c>
+      <c r="C4" s="99" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>85</v>
+      </c>
+      <c r="F4">
+        <v>8.5</v>
+      </c>
+      <c r="I4" s="99" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="72" customFormat="1">
+      <c r="A5" s="99" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="100">
+        <v>46063</v>
+      </c>
+      <c r="C5" s="99" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="72">
+        <v>2</v>
+      </c>
+      <c r="E5" s="72">
+        <v>119</v>
+      </c>
+      <c r="F5" s="72">
+        <v>333.2</v>
+      </c>
+      <c r="I5" s="99" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="100">
+        <v>46127</v>
+      </c>
+      <c r="C6" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="72">
+        <v>1</v>
+      </c>
+      <c r="E6" s="72">
+        <v>118</v>
+      </c>
+      <c r="F6" s="72">
+        <v>330.4</v>
+      </c>
+      <c r="I6" s="99" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="99" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="100">
+        <v>46135</v>
+      </c>
+      <c r="C7" s="72" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>305</v>
+      </c>
+      <c r="F7" s="72">
+        <v>854</v>
+      </c>
+      <c r="I7" s="99" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="99"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="98" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="98" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="98" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>